--- a/PoCat3_Thermal_Model_Mass_Properties.xlsx
+++ b/PoCat3_Thermal_Model_Mass_Properties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oscar\Documents\GitHub\PoCat-Thermal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8041057C-619F-47FC-B322-1D5207889C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D34766-4BA0-4650-9014-843B04E51305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
